--- a/Sumaco/Sumaco_LA.xlsx
+++ b/Sumaco/Sumaco_LA.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="50">
   <si>
     <t>Plot</t>
   </si>
@@ -169,21 +169,6 @@
   </si>
   <si>
     <t>3770</t>
-  </si>
-  <si>
-    <t>Sum11_3697</t>
-  </si>
-  <si>
-    <t>Sum9_3728</t>
-  </si>
-  <si>
-    <t>edit_Sum9_3735</t>
-  </si>
-  <si>
-    <t>edit_sum11_3695 6 hojas compuestas ery</t>
-  </si>
-  <si>
-    <t>sum10_3723</t>
   </si>
 </sst>
 </file>
@@ -244,12 +229,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -554,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11.85546875" customWidth="1"/>
@@ -1147,43 +1135,123 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C43" s="2" t="s">
-        <v>50</v>
+      <c r="A43" s="1">
+        <v>11</v>
+      </c>
+      <c r="B43">
+        <v>11</v>
+      </c>
+      <c r="C43" s="2">
+        <v>3697</v>
       </c>
       <c r="D43" s="2">
         <v>847.49129400000004</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C44" s="2" t="s">
-        <v>51</v>
+      <c r="A44" s="1">
+        <v>12</v>
+      </c>
+      <c r="B44">
+        <v>9</v>
+      </c>
+      <c r="C44" s="2">
+        <v>3728</v>
       </c>
       <c r="D44" s="2">
         <v>1398.307</v>
       </c>
     </row>
-    <row r="45" spans="1:4" ht="24" x14ac:dyDescent="0.25">
-      <c r="C45" s="2" t="s">
-        <v>52</v>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>13</v>
+      </c>
+      <c r="B45">
+        <v>9</v>
+      </c>
+      <c r="C45" s="2">
+        <v>3735</v>
       </c>
       <c r="D45" s="2">
         <v>2732.261</v>
       </c>
     </row>
-    <row r="46" spans="1:4" ht="48" x14ac:dyDescent="0.25">
-      <c r="C46" s="2" t="s">
-        <v>53</v>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>14</v>
+      </c>
+      <c r="B46">
+        <v>11</v>
+      </c>
+      <c r="C46" s="2">
+        <v>3695</v>
       </c>
       <c r="D46" s="2">
         <v>3060.808</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C47" s="2" t="s">
-        <v>54</v>
+      <c r="A47" s="1">
+        <v>15</v>
+      </c>
+      <c r="B47">
+        <v>10</v>
+      </c>
+      <c r="C47" s="2">
+        <v>3723</v>
       </c>
       <c r="D47" s="2">
         <v>899.24099999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>16</v>
+      </c>
+      <c r="B48">
+        <v>10</v>
+      </c>
+      <c r="C48">
+        <v>3725</v>
+      </c>
+      <c r="D48" s="3">
+        <v>1055.4580000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>17</v>
+      </c>
+      <c r="B49">
+        <v>10</v>
+      </c>
+      <c r="C49">
+        <v>3708</v>
+      </c>
+      <c r="D49" s="3">
+        <v>1359.0329999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>18</v>
+      </c>
+      <c r="B50">
+        <v>11</v>
+      </c>
+      <c r="C50">
+        <v>3707</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>19</v>
+      </c>
+      <c r="B51">
+        <v>18</v>
+      </c>
+      <c r="C51">
+        <v>3767</v>
       </c>
     </row>
   </sheetData>
